--- a/salidas/empresas/TSLA.xlsx
+++ b/salidas/empresas/TSLA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B16" t="n">
@@ -773,7 +785,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B17" t="n">
@@ -798,7 +810,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B18" t="n">
@@ -823,7 +835,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B19" t="n">
@@ -848,7 +860,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B20" t="n">
@@ -873,7 +885,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B21" t="n">
@@ -898,7 +910,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B22" t="n">
@@ -923,7 +935,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B23" t="n">
@@ -948,7 +960,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B24" t="n">
@@ -973,7 +985,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B25" t="n">
@@ -998,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B26" t="n">
@@ -1023,7 +1035,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B27" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B28" t="n">
@@ -1073,7 +1085,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B29" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B30" t="n">
@@ -1123,7 +1135,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B32" t="n">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B33" t="n">
@@ -1198,7 +1210,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B34" t="n">
@@ -1223,7 +1235,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B35" t="n">
@@ -1248,7 +1260,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B36" t="n">
@@ -1273,7 +1285,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B37" t="n">
@@ -1298,7 +1310,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B38" t="n">
@@ -1323,7 +1335,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B39" t="n">
@@ -1348,7 +1360,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B40" t="n">
@@ -1373,7 +1385,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B41" t="n">
@@ -1398,7 +1410,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B42" t="n">
@@ -1423,7 +1435,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B43" t="n">
@@ -1448,7 +1460,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B44" t="n">
@@ -1473,7 +1485,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B45" t="n">
@@ -1498,7 +1510,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B46" t="n">
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B47" t="n">
@@ -1548,7 +1560,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B48" t="n">
@@ -1573,7 +1585,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B49" t="n">
@@ -1598,7 +1610,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B50" t="n">
@@ -1623,7 +1635,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B51" t="n">
@@ -1648,7 +1660,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B52" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B53" t="n">
@@ -1698,7 +1710,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B54" t="n">
@@ -1723,7 +1735,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B55" t="n">
@@ -1748,7 +1760,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B56" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B57" t="n">
@@ -1798,7 +1810,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B58" t="n">
@@ -1825,7 +1837,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B59" t="n">
@@ -1852,7 +1864,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B60" t="n">
@@ -1879,7 +1891,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B61" t="n">
@@ -1906,7 +1918,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B62" t="n">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B63" t="n">
@@ -1960,7 +1972,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B64" t="n">
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B65" t="n">
@@ -2014,7 +2026,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B66" t="n">
@@ -2041,7 +2053,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B67" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B68" t="n">
@@ -2095,7 +2107,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B69" t="n">
@@ -2122,7 +2134,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B70" t="n">
@@ -2149,7 +2161,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B71" t="n">
@@ -2174,7 +2186,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B72" t="n">
@@ -2199,7 +2211,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B73" t="n">
@@ -2224,7 +2236,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B74" t="n">
@@ -2249,7 +2261,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B75" t="n">
@@ -2274,7 +2286,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B76" t="n">
@@ -2299,7 +2311,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B77" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B78" t="n">
@@ -2349,7 +2361,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B79" t="n">
@@ -2376,7 +2388,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B80" t="n">
@@ -2403,7 +2415,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B81" t="n">
@@ -2430,7 +2442,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B82" t="n">
@@ -2457,7 +2469,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B83" t="n">
@@ -2484,7 +2496,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B84" t="n">
@@ -2511,7 +2523,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B85" t="n">
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B86" t="n">
@@ -2563,7 +2575,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B87" t="n">
@@ -2588,7 +2600,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B88" t="n">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B89" t="n">
@@ -2638,7 +2650,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B90" t="n">
@@ -2663,7 +2675,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B91" t="n">
@@ -2688,7 +2700,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B92" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B93" t="n">
@@ -2738,7 +2750,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B94" t="n">
@@ -2765,7 +2777,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B95" t="n">
@@ -2792,7 +2804,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B96" t="n">
@@ -2819,7 +2831,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B97" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B98" t="n">
@@ -2873,7 +2885,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B99" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B100" t="n">
@@ -2927,7 +2939,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B101" t="n">
@@ -2954,7 +2966,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B102" t="n">
@@ -2981,7 +2993,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B103" t="n">
@@ -3008,7 +3020,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B104" t="n">
@@ -3035,7 +3047,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B105" t="n">
@@ -3062,7 +3074,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B106" t="n">
@@ -3089,7 +3101,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B107" t="n">
@@ -3116,7 +3128,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B108" t="n">
@@ -3143,7 +3155,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B109" t="n">
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B110" t="n">
@@ -3197,7 +3209,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B111" t="n">
@@ -3224,7 +3236,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B112" t="n">
@@ -3251,7 +3263,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B113" t="n">
@@ -3278,7 +3290,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B114" t="n">
@@ -3305,7 +3317,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B115" t="n">
@@ -3332,7 +3344,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B116" t="n">
@@ -3359,7 +3371,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B117" t="n">
@@ -3386,7 +3398,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B118" t="n">
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B119" t="n">
@@ -3440,7 +3452,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B120" t="n">
@@ -3467,7 +3479,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B121" t="n">
@@ -3494,7 +3506,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B122" t="n">
@@ -3521,7 +3533,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B123" t="n">
@@ -3550,7 +3562,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B124" t="n">
@@ -3579,7 +3591,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B125" t="n">
@@ -3608,7 +3620,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B126" t="n">
@@ -3637,7 +3649,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B127" t="n">
@@ -3666,7 +3678,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B128" t="n">
@@ -3695,7 +3707,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B129" t="n">
@@ -3724,7 +3736,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B130" t="n">
@@ -3753,7 +3765,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B131" t="n">
@@ -3782,7 +3794,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B132" t="n">
@@ -3811,7 +3823,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B133" t="n">
@@ -3840,7 +3852,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B134" t="n">
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B135" t="n">
@@ -3898,7 +3910,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B136" t="n">
@@ -3927,7 +3939,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B137" t="n">
@@ -3956,7 +3968,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B138" t="n">
@@ -3985,7 +3997,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B139" t="n">
@@ -4014,7 +4026,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B140" t="n">
@@ -4043,7 +4055,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B141" t="n">
@@ -4072,7 +4084,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B142" t="n">
@@ -4101,7 +4113,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B143" t="n">
@@ -4130,7 +4142,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B144" t="n">
@@ -4159,7 +4171,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B145" t="n">
@@ -4188,7 +4200,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B146" t="n">
@@ -4217,7 +4229,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B147" t="n">
@@ -4246,7 +4258,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B148" t="n">
@@ -4275,7 +4287,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B149" t="n">
@@ -4304,7 +4316,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B150" t="n">
@@ -4333,7 +4345,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B151" t="n">
@@ -4362,7 +4374,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B152" t="n">
@@ -4391,7 +4403,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B153" t="n">
@@ -4420,7 +4432,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B154" t="n">
@@ -4449,7 +4461,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B155" t="n">
@@ -4478,7 +4490,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B156" t="n">
@@ -4507,7 +4519,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B157" t="n">
@@ -4536,7 +4548,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B158" t="n">
@@ -4565,7 +4577,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B159" t="n">
@@ -4594,7 +4606,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B160" t="n">
@@ -4623,7 +4635,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B161" t="n">
@@ -4652,7 +4664,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B162" t="n">
@@ -4681,7 +4693,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B163" t="n">
@@ -4710,7 +4722,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B164" t="n">
@@ -4739,7 +4751,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B165" t="n">
@@ -4768,7 +4780,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B166" t="n">
@@ -4797,7 +4809,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B167" t="n">
@@ -4826,7 +4838,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B168" t="n">
@@ -4855,7 +4867,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B169" t="n">
@@ -4884,7 +4896,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B170" t="n">
@@ -4913,7 +4925,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B171" t="n">
@@ -4942,7 +4954,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B172" t="n">
@@ -4971,7 +4983,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B173" t="n">
@@ -5000,7 +5012,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B174" t="n">
@@ -5029,7 +5041,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B175" t="n">
@@ -5058,7 +5070,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B176" t="n">
@@ -5087,7 +5099,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B177" t="n">
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B178" t="n">
@@ -5145,7 +5157,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B179" t="n">
@@ -5174,7 +5186,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B180" t="n">
@@ -5203,7 +5215,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B181" t="n">
@@ -5232,7 +5244,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B182" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B183" t="n">
@@ -5290,7 +5302,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B184" t="n">
@@ -5319,7 +5331,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B185" t="n">
@@ -5348,7 +5360,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B186" t="n">
@@ -5377,7 +5389,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B187" t="n">
@@ -5406,7 +5418,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B188" t="n">
@@ -5435,7 +5447,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B189" t="n">
@@ -5464,7 +5476,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B190" t="n">
@@ -5493,7 +5505,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B191" t="n">
@@ -5522,7 +5534,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B192" t="n">
@@ -5551,7 +5563,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B193" t="n">
@@ -5580,7 +5592,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B194" t="n">
@@ -5609,7 +5621,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B195" t="n">
@@ -5638,7 +5650,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B196" t="n">
@@ -5667,32 +5679,32 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B197" t="n">
-        <v>380.1199951171875</v>
+        <v>377.9400024414062</v>
       </c>
       <c r="C197" t="n">
-        <v>380.1199951171875</v>
+        <v>377.9400024414062</v>
       </c>
       <c r="D197" t="n">
-        <v>626303900</v>
+        <v>652487000</v>
       </c>
       <c r="E197" t="n">
         <v>1.08</v>
       </c>
       <c r="F197" t="n">
-        <v>351.9629584418403</v>
+        <v>349.9444467050058</v>
       </c>
       <c r="G197" t="n">
         <v>3949547394</v>
       </c>
       <c r="H197" t="n">
-        <v>1501301936122.381</v>
+        <v>1492691951730.81</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1585761196210626</v>
+        <v>0.1652055121534263</v>
       </c>
     </row>
   </sheetData>
@@ -5724,75 +5736,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5828,13 +5840,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5870,13 +5882,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5912,13 +5924,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5954,13 +5966,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5987,7 +5999,7 @@
       <c r="I6" t="n">
         <v>-0.04133333333333333</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K6" t="n">
@@ -6000,13 +6012,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6033,7 +6045,7 @@
       <c r="I7" t="n">
         <v>-0.068</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K7" t="n">
@@ -6046,13 +6058,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6079,7 +6091,7 @@
       <c r="I8" t="n">
         <v>-0.08399999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K8" t="n">
@@ -6092,13 +6104,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6125,7 +6137,7 @@
       <c r="I9" t="n">
         <v>-0.1026666666666667</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K9" t="n">
@@ -6138,13 +6150,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6171,7 +6183,7 @@
       <c r="I10" t="n">
         <v>-0.1573333333333333</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K10" t="n">
@@ -6184,13 +6196,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6217,7 +6229,7 @@
       <c r="I11" t="n">
         <v>-0.212</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="K11" t="n">
@@ -6230,13 +6242,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6263,7 +6275,7 @@
       <c r="I12" t="n">
         <v>-0.2753333333333333</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K12" t="n">
@@ -6276,13 +6288,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6309,7 +6321,7 @@
       <c r="I13" t="n">
         <v>-0.354</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K13" t="n">
@@ -6322,13 +6334,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6355,7 +6367,7 @@
       <c r="I14" t="n">
         <v>-0.462</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K14" t="n">
@@ -6368,13 +6380,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6401,7 +6413,7 @@
       <c r="I15" t="n">
         <v>-0.5226666666666666</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K15" t="n">
@@ -6414,13 +6426,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6447,7 +6459,7 @@
       <c r="I16" t="n">
         <v>-0.5653333333333332</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K16" t="n">
@@ -6460,13 +6472,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6493,7 +6505,7 @@
       <c r="I17" t="n">
         <v>-0.4373333333333333</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K17" t="n">
@@ -6506,13 +6518,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6539,7 +6551,7 @@
       <c r="I18" t="n">
         <v>-0.3120000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K18" t="n">
@@ -6552,13 +6564,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6585,7 +6597,7 @@
       <c r="I19" t="n">
         <v>-0.306</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="K19" t="n">
@@ -6598,13 +6610,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6631,7 +6643,7 @@
       <c r="I20" t="n">
         <v>-0.3026666666666668</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K20" t="n">
@@ -6644,13 +6656,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6677,7 +6689,7 @@
       <c r="I21" t="n">
         <v>-0.5586666666666668</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K21" t="n">
@@ -6690,13 +6702,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6723,7 +6735,7 @@
       <c r="I22" t="n">
         <v>-0.790287543688188</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K22" t="n">
@@ -6736,13 +6748,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6769,7 +6781,7 @@
       <c r="I23" t="n">
         <v>-0.9336208770215214</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K23" t="n">
@@ -6782,13 +6794,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6815,7 +6827,7 @@
       <c r="I24" t="n">
         <v>-1.078954210354855</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K24" t="n">
@@ -6828,13 +6840,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6861,7 +6873,7 @@
       <c r="I25" t="n">
         <v>-0.7156208770215213</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K25" t="n">
@@ -6874,13 +6886,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6907,7 +6919,7 @@
       <c r="I26" t="n">
         <v>-0.3813333333333334</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="K26" t="n">
@@ -6920,13 +6932,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6953,7 +6965,7 @@
       <c r="I27" t="n">
         <v>-0.3753333333333334</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="K27" t="n">
@@ -6966,13 +6978,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6999,7 +7011,7 @@
       <c r="I28" t="n">
         <v>-0.248</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="K28" t="n">
@@ -7012,13 +7024,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7045,7 +7057,7 @@
       <c r="I29" t="n">
         <v>-0.3126666666666667</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K29" t="n">
@@ -7058,13 +7070,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7091,7 +7103,7 @@
       <c r="I30" t="n">
         <v>-0.328</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K30" t="n">
@@ -7104,13 +7116,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7137,7 +7149,7 @@
       <c r="I31" t="n">
         <v>-0.04933333333333335</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K31" t="n">
@@ -7150,13 +7162,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7183,7 +7195,7 @@
       <c r="I32" t="n">
         <v>0.138</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K32" t="n">
@@ -7196,13 +7208,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44130</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7229,7 +7241,7 @@
       <c r="I33" t="n">
         <v>0.176</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44130</v>
       </c>
       <c r="K33" t="n">
@@ -7242,13 +7254,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7275,7 +7287,7 @@
       <c r="I34" t="n">
         <v>0.2133333333333333</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="K34" t="n">
@@ -7288,13 +7300,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7321,7 +7333,7 @@
       <c r="I35" t="n">
         <v>0.338</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K35" t="n">
@@ -7334,13 +7346,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7367,7 +7379,7 @@
       <c r="I36" t="n">
         <v>0.6446666666666667</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K36" t="n">
@@ -7380,13 +7392,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7413,7 +7425,7 @@
       <c r="I37" t="n">
         <v>1.034666666666667</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="K37" t="n">
@@ -7426,13 +7438,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7459,7 +7471,7 @@
       <c r="I38" t="n">
         <v>1.633333333333334</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K38" t="n">
@@ -7472,13 +7484,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44676</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7505,7 +7517,7 @@
       <c r="I39" t="n">
         <v>2.456666666666667</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44676</v>
       </c>
       <c r="K39" t="n">
@@ -7518,13 +7530,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7551,7 +7563,7 @@
       <c r="I40" t="n">
         <v>2.766666666666667</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="K40" t="n">
@@ -7564,13 +7576,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7597,7 +7609,7 @@
       <c r="I41" t="n">
         <v>3.236666666666667</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="K41" t="n">
@@ -7610,13 +7622,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7643,7 +7655,7 @@
       <c r="I42" t="n">
         <v>3.62</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="K42" t="n">
@@ -7656,13 +7668,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7689,7 +7701,7 @@
       <c r="I43" t="n">
         <v>3.396666666666667</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="K43" t="n">
@@ -7702,13 +7714,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7735,7 +7747,7 @@
       <c r="I44" t="n">
         <v>3.526666666666667</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="K44" t="n">
@@ -7748,13 +7760,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7781,7 +7793,7 @@
       <c r="I45" t="n">
         <v>3.106666666666667</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="K45" t="n">
@@ -7794,13 +7806,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7827,7 +7839,7 @@
       <c r="I46" t="n">
         <v>4.3</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="K46" t="n">
@@ -7840,13 +7852,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7873,7 +7885,7 @@
       <c r="I47" t="n">
         <v>3.91</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K47" t="n">
@@ -7886,13 +7898,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7919,7 +7931,7 @@
       <c r="I48" t="n">
         <v>3.55</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="K48" t="n">
@@ -7932,13 +7944,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7965,7 +7977,7 @@
       <c r="I49" t="n">
         <v>3.64</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K49" t="n">
@@ -7978,13 +7990,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8011,7 +8023,7 @@
       <c r="I50" t="n">
         <v>2.04</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="K50" t="n">
@@ -8024,13 +8036,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8057,7 +8069,7 @@
       <c r="I51" t="n">
         <v>1.82</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K51" t="n">
@@ -8070,13 +8082,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8103,7 +8115,7 @@
       <c r="I52" t="n">
         <v>1.73</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K52" t="n">
@@ -8116,13 +8128,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8149,7 +8161,7 @@
       <c r="I53" t="n">
         <v>1.5</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K53" t="n">
@@ -8162,13 +8174,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8195,7 +8207,7 @@
       <c r="I54" t="n">
         <v>1.08</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K54" t="n">
@@ -8208,13 +8220,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8241,7 +8253,7 @@
       <c r="I55" t="n">
         <v>1.09</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K55" t="n">
@@ -8254,13 +8266,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8287,7 +8299,7 @@
       <c r="I56" t="n">
         <v>1.08</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K56" t="n">
@@ -8324,52 +8336,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40767</v>
       </c>
       <c r="C2" t="n">
@@ -8398,10 +8410,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40861</v>
       </c>
       <c r="C3" t="n">
@@ -8430,10 +8442,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C4" t="n">
@@ -8462,10 +8474,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="C5" t="n">
@@ -8494,10 +8506,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C6" t="n">
@@ -8526,10 +8538,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C7" t="n">
@@ -8558,10 +8570,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41340</v>
       </c>
       <c r="C8" t="n">
@@ -8590,10 +8602,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="C9" t="n">
@@ -8622,10 +8634,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41495</v>
       </c>
       <c r="C10" t="n">
@@ -8654,10 +8666,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C11" t="n">
@@ -8686,10 +8698,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C12" t="n">
@@ -8718,10 +8730,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="C13" t="n">
@@ -8750,10 +8762,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C14" t="n">
@@ -8782,10 +8794,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C15" t="n">
@@ -8814,10 +8826,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C16" t="n">
@@ -8846,10 +8858,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="C17" t="n">
@@ -8878,10 +8890,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42215</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C18" t="n">
@@ -8910,10 +8922,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42306</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C19" t="n">
@@ -8942,10 +8954,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C20" t="n">
@@ -8974,10 +8986,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C21" t="n">
@@ -9006,10 +9018,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C22" t="n">
@@ -9038,10 +9050,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42668</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C23" t="n">
@@ -9070,10 +9082,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C24" t="n">
@@ -9102,10 +9114,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="C25" t="n">
@@ -9134,10 +9146,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C26" t="n">
@@ -9166,10 +9178,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C27" t="n">
@@ -9198,10 +9210,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43145</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C28" t="n">
@@ -9230,10 +9242,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43227</v>
       </c>
       <c r="C29" t="n">
@@ -9262,10 +9274,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C30" t="n">
@@ -9294,10 +9306,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C31" t="n">
@@ -9326,10 +9338,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43508</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C32" t="n">
@@ -9358,10 +9370,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43577</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="C33" t="n">
@@ -9390,10 +9402,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="C34" t="n">
@@ -9422,10 +9434,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C35" t="n">
@@ -9454,10 +9466,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C36" t="n">
@@ -9486,10 +9498,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43944</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C37" t="n">
@@ -9518,10 +9530,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C38" t="n">
@@ -9550,10 +9562,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44124</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44130</v>
       </c>
       <c r="C39" t="n">
@@ -9582,10 +9594,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="C40" t="n">
@@ -9614,10 +9626,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44307</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C41" t="n">
@@ -9646,10 +9658,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44399</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C42" t="n">
@@ -9678,10 +9690,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="C43" t="n">
@@ -9710,10 +9722,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="C44" t="n">
@@ -9742,10 +9754,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44670</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44676</v>
       </c>
       <c r="C45" t="n">
@@ -9774,10 +9786,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44761</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="C46" t="n">
@@ -9806,10 +9818,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44852</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="C47" t="n">
@@ -9838,10 +9850,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44951</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="C48" t="n">
@@ -9870,10 +9882,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45033</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="C49" t="n">
@@ -9902,10 +9914,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="C50" t="n">
@@ -9934,10 +9946,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="C51" t="n">
@@ -9966,10 +9978,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45313</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="C52" t="n">
@@ -9998,10 +10010,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C53" t="n">
@@ -10030,10 +10042,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C54" t="n">
@@ -10062,10 +10074,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C55" t="n">
@@ -10094,10 +10106,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45679</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="C56" t="n">
@@ -10126,10 +10138,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C57" t="n">
@@ -10158,10 +10170,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C58" t="n">
@@ -10190,10 +10202,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45946</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C59" t="n">
@@ -10222,10 +10234,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C60" t="n">
@@ -10254,10 +10266,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C61" t="n">
@@ -10286,10 +10298,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C62" t="n">
@@ -10336,12 +10348,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
